--- a/src/PRODUTOS.xlsx
+++ b/src/PRODUTOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\bot_cadastrar\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALGOMAIS\Desktop\testes\BOT_CADASTRAR\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77657DC-7807-4647-B674-02083D8573C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E9E108-FEFC-4BF3-85CC-BF87BCD74692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="0" windowWidth="5160" windowHeight="12900" xr2:uid="{91E8BF43-8DB8-4257-B6FB-93A082320184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{91E8BF43-8DB8-4257-B6FB-93A082320184}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -216,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -256,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -362,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/src/PRODUTOS.xlsx
+++ b/src/PRODUTOS.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28626"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALGOMAIS\Desktop\testes\BOT_CADASTRAR\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Algo Mais Nova\Desktop\BOT_CADASTRAR\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E9E108-FEFC-4BF3-85CC-BF87BCD74692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{91E8BF43-8DB8-4257-B6FB-93A082320184}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>nome</t>
   </si>
@@ -43,50 +41,111 @@
     <t>codigo de barra</t>
   </si>
   <si>
-    <t>valor de venda</t>
-  </si>
-  <si>
-    <t>estoque-min</t>
-  </si>
-  <si>
-    <t>estoque-max</t>
-  </si>
-  <si>
-    <t>estoque-atual</t>
-  </si>
-  <si>
-    <t>PRODUTO TESTE 2</t>
-  </si>
-  <si>
-    <t>PRODUTO TESTE 3</t>
-  </si>
-  <si>
-    <t>PRODUTO TESTE 4</t>
-  </si>
-  <si>
-    <t>PRODUTO TESTE 5</t>
-  </si>
-  <si>
-    <t>PRODUTO 1 EXEMPLO</t>
-  </si>
-  <si>
-    <t>CABO PRODUTO 1 EXEMPLO</t>
-  </si>
-  <si>
-    <t>CARREGADOR PRODUTO 1 EXEMPLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABO PRODUTO 1 EXEMPLO PARA IOS </t>
+    <t>IPHONE 5</t>
+  </si>
+  <si>
+    <t>IPHONE 6</t>
+  </si>
+  <si>
+    <t>FUTURAMENTE</t>
+  </si>
+  <si>
+    <t>est_3d</t>
+  </si>
+  <si>
+    <t>est_ceramica</t>
+  </si>
+  <si>
+    <t>est_privada</t>
+  </si>
+  <si>
+    <t>est_ceramica_privada</t>
+  </si>
+  <si>
+    <t>IPHONE 3</t>
+  </si>
+  <si>
+    <t>IPHONE 4</t>
+  </si>
+  <si>
+    <t>IPHONE 7</t>
+  </si>
+  <si>
+    <t>IPHONE 8</t>
+  </si>
+  <si>
+    <t>IPHONE 9</t>
+  </si>
+  <si>
+    <t>IPHONE 10</t>
+  </si>
+  <si>
+    <t>IPHONE 11</t>
+  </si>
+  <si>
+    <t>SAMSUNG A01</t>
+  </si>
+  <si>
+    <t>SAMSUNG A02</t>
+  </si>
+  <si>
+    <t>SAMSUNG A03</t>
+  </si>
+  <si>
+    <t>SAMSUNG A04</t>
+  </si>
+  <si>
+    <t>SAMSUNG A05</t>
+  </si>
+  <si>
+    <t>SAMSUNG A06</t>
+  </si>
+  <si>
+    <t>SAMSUNG A07</t>
+  </si>
+  <si>
+    <t>SAMSUNG A08</t>
+  </si>
+  <si>
+    <t>SAMSUNG A09</t>
+  </si>
+  <si>
+    <t>SAMSUNG A10</t>
+  </si>
+  <si>
+    <t>MOTOROLA G6</t>
+  </si>
+  <si>
+    <t>MOTOROLA G7</t>
+  </si>
+  <si>
+    <t>MOTOROLA G8</t>
+  </si>
+  <si>
+    <t>MOTOROLA G9</t>
+  </si>
+  <si>
+    <t>MOTOROLA G10</t>
+  </si>
+  <si>
+    <t>MOTOROLA G11</t>
+  </si>
+  <si>
+    <t>MOTOROLA G12</t>
+  </si>
+  <si>
+    <t>MOTOROLA G13</t>
+  </si>
+  <si>
+    <t>MOTOROLA G14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="165" formatCode="[$R$ -416]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -97,36 +156,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -187,17 +246,31 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,214 +584,449 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA2D2EA-DF44-4138-9EAB-DDE1A9638F23}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6">
-        <v>10</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5">
-        <v>5</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>40</v>
-      </c>
-      <c r="F3" s="5">
-        <v>40</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9">
-        <v>6989652331394</v>
-      </c>
-      <c r="C4">
-        <v>65</v>
-      </c>
-      <c r="D4" s="9">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9">
-        <v>10</v>
-      </c>
-      <c r="F4" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9">
-        <v>7908125203340</v>
-      </c>
-      <c r="C5">
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="9">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9">
-        <v>20</v>
-      </c>
-      <c r="F5" s="9">
-        <v>20</v>
-      </c>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="B20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B34" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B35" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B36" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B37" s="9" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE908C4A-7A47-4BE4-941A-FE59A69906E5}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2">
-        <v>23456789</v>
-      </c>
-      <c r="C1" s="2">
-        <v>50</v>
-      </c>
-      <c r="D1" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2">
-        <v>50</v>
-      </c>
-      <c r="F1" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2">
-        <v>60</v>
-      </c>
-      <c r="F3" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2">
-        <v>12345677</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/src/PRODUTOS.xlsx
+++ b/src/PRODUTOS.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="118">
   <si>
     <t>nome</t>
   </si>
@@ -41,12 +41,6 @@
     <t>codigo de barra</t>
   </si>
   <si>
-    <t>IPHONE 5</t>
-  </si>
-  <si>
-    <t>IPHONE 6</t>
-  </si>
-  <si>
     <t>FUTURAMENTE</t>
   </si>
   <si>
@@ -62,82 +56,337 @@
     <t>est_ceramica_privada</t>
   </si>
   <si>
-    <t>IPHONE 3</t>
-  </si>
-  <si>
-    <t>IPHONE 4</t>
-  </si>
-  <si>
-    <t>IPHONE 7</t>
-  </si>
-  <si>
-    <t>IPHONE 8</t>
-  </si>
-  <si>
-    <t>IPHONE 9</t>
-  </si>
-  <si>
-    <t>IPHONE 10</t>
-  </si>
-  <si>
-    <t>IPHONE 11</t>
-  </si>
-  <si>
-    <t>SAMSUNG A01</t>
-  </si>
-  <si>
-    <t>SAMSUNG A02</t>
-  </si>
-  <si>
-    <t>SAMSUNG A03</t>
-  </si>
-  <si>
-    <t>SAMSUNG A04</t>
-  </si>
-  <si>
-    <t>SAMSUNG A05</t>
-  </si>
-  <si>
-    <t>SAMSUNG A06</t>
-  </si>
-  <si>
-    <t>SAMSUNG A07</t>
-  </si>
-  <si>
-    <t>SAMSUNG A08</t>
-  </si>
-  <si>
-    <t>SAMSUNG A09</t>
-  </si>
-  <si>
-    <t>SAMSUNG A10</t>
-  </si>
-  <si>
-    <t>MOTOROLA G6</t>
-  </si>
-  <si>
-    <t>MOTOROLA G7</t>
-  </si>
-  <si>
-    <t>MOTOROLA G8</t>
-  </si>
-  <si>
-    <t>MOTOROLA G9</t>
-  </si>
-  <si>
-    <t>MOTOROLA G10</t>
-  </si>
-  <si>
-    <t>MOTOROLA G11</t>
-  </si>
-  <si>
-    <t>MOTOROLA G12</t>
-  </si>
-  <si>
-    <t>MOTOROLA G13</t>
-  </si>
-  <si>
-    <t>MOTOROLA G14</t>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>J2 CORE</t>
+  </si>
+  <si>
+    <t>J2 PRIME</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>J4 PLUS</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>J5 PRO</t>
+  </si>
+  <si>
+    <t>J5 PRIME</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>J6 PLUS</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>J7 PRO</t>
+  </si>
+  <si>
+    <t>J7 PRIME</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>J8 PLUS</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>A01 CORE</t>
+  </si>
+  <si>
+    <t>A02/A02S/A03</t>
+  </si>
+  <si>
+    <t>A04/04E/A04S</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A05S</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10/A10S</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13 - 4G/5G</t>
+  </si>
+  <si>
+    <t>A14/M14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A20/A30</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A20S</t>
+  </si>
+  <si>
+    <t>A21/A21S</t>
+  </si>
+  <si>
+    <t>A22 - 4G</t>
+  </si>
+  <si>
+    <t>A22 -5G</t>
+  </si>
+  <si>
+    <t>A23 - 4G/5G</t>
+  </si>
+  <si>
+    <t>A24</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>A30S</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>A32 - 4G</t>
+  </si>
+  <si>
+    <t>A32 - 5G</t>
+  </si>
+  <si>
+    <t>A33</t>
+  </si>
+  <si>
+    <t>A34</t>
+  </si>
+  <si>
+    <t>A35/A55</t>
+  </si>
+  <si>
+    <t>A50</t>
+  </si>
+  <si>
+    <t>A51</t>
+  </si>
+  <si>
+    <t>A52</t>
+  </si>
+  <si>
+    <t>A53</t>
+  </si>
+  <si>
+    <t>A54</t>
+  </si>
+  <si>
+    <t>A60</t>
+  </si>
+  <si>
+    <t>A62</t>
+  </si>
+  <si>
+    <t>A70</t>
+  </si>
+  <si>
+    <t>A63</t>
+  </si>
+  <si>
+    <t>A71</t>
+  </si>
+  <si>
+    <t>A72</t>
+  </si>
+  <si>
+    <t>A73</t>
+  </si>
+  <si>
+    <t>A80/A90</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>M23</t>
+  </si>
+  <si>
+    <t>M30</t>
+  </si>
+  <si>
+    <t>M31S</t>
+  </si>
+  <si>
+    <t>M32</t>
+  </si>
+  <si>
+    <t>M33</t>
+  </si>
+  <si>
+    <t>M34</t>
+  </si>
+  <si>
+    <t>M35 - 5G</t>
+  </si>
+  <si>
+    <t>M51</t>
+  </si>
+  <si>
+    <t>M52</t>
+  </si>
+  <si>
+    <t>M53</t>
+  </si>
+  <si>
+    <t>M54</t>
+  </si>
+  <si>
+    <t>M55</t>
+  </si>
+  <si>
+    <t>M62</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>S9</t>
+  </si>
+  <si>
+    <t>S9 PLUS</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10 E </t>
+  </si>
+  <si>
+    <t>S10 LITE</t>
+  </si>
+  <si>
+    <t>S10 PLUS</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>S20 FE</t>
+  </si>
+  <si>
+    <t>S20 ULTRA</t>
+  </si>
+  <si>
+    <t>S20 PLUS</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>S21 FE</t>
+  </si>
+  <si>
+    <t>S21 ULTRA</t>
+  </si>
+  <si>
+    <t>S21 PLUS</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>S22 PLUS</t>
+  </si>
+  <si>
+    <t>S22 ULTRA</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>S23 FE</t>
+  </si>
+  <si>
+    <t>S23 ULTRA</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>S24 PLUS</t>
+  </si>
+  <si>
+    <t>S24 ULTRA</t>
+  </si>
+  <si>
+    <t>A31S</t>
+  </si>
+  <si>
+    <t>S24 FE</t>
+  </si>
+  <si>
+    <t>S23 PLUS</t>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M31</t>
+  </si>
+  <si>
+    <t>NOTE 20</t>
   </si>
 </sst>
 </file>
@@ -202,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -225,51 +474,41 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.140625" customWidth="1"/>
@@ -597,432 +836,1375 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="B14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="B16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="B17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="B18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="B19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="B20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="B21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+    </row>
+    <row r="32" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="34" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="B34" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B35" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="35" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="B36" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="2:6" ht="23.25" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+    </row>
+    <row r="37" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="B37" s="9" t="s">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="38" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="39" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+    </row>
+    <row r="40" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A45" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A46" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A49" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A51" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+    </row>
+    <row r="52" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+    </row>
+    <row r="53" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+    </row>
+    <row r="55" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+    </row>
+    <row r="56" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A56" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+    </row>
+    <row r="57" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+    </row>
+    <row r="58" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A58" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+    </row>
+    <row r="59" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A59" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+    </row>
+    <row r="60" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A60" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+    </row>
+    <row r="61" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A61" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+    </row>
+    <row r="62" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A62" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+    </row>
+    <row r="63" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A63" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+    </row>
+    <row r="64" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A64" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+    </row>
+    <row r="65" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A65" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+    </row>
+    <row r="66" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A66" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+    </row>
+    <row r="67" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A67" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+    </row>
+    <row r="68" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A68" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+    </row>
+    <row r="69" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+    </row>
+    <row r="70" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+    </row>
+    <row r="71" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+    </row>
+    <row r="72" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+    </row>
+    <row r="73" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A73" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+    </row>
+    <row r="74" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+    </row>
+    <row r="75" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+    </row>
+    <row r="76" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+    </row>
+    <row r="77" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+    </row>
+    <row r="78" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A78" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+    </row>
+    <row r="79" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A79" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+    </row>
+    <row r="80" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A80" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+    </row>
+    <row r="81" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A81" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+    </row>
+    <row r="82" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A82" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+    </row>
+    <row r="83" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A83" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+    </row>
+    <row r="84" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A84" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+    </row>
+    <row r="85" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A85" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+    </row>
+    <row r="86" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A86" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+    </row>
+    <row r="87" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A87" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+    </row>
+    <row r="88" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A88" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+    </row>
+    <row r="89" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A89" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+    </row>
+    <row r="90" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A90" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+    </row>
+    <row r="91" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A91" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+    </row>
+    <row r="92" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A92" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+    </row>
+    <row r="93" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A93" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+    </row>
+    <row r="94" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A94" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+    </row>
+    <row r="95" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A95" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+    </row>
+    <row r="96" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A96" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+    </row>
+    <row r="97" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A97" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+    </row>
+    <row r="98" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A98" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+    </row>
+    <row r="99" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A99" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+    </row>
+    <row r="100" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A100" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+    </row>
+    <row r="101" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A101" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+    </row>
+    <row r="102" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A102" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+    </row>
+    <row r="103" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A103" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+    </row>
+    <row r="104" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A104" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
+    </row>
+    <row r="105" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A105" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+    </row>
+    <row r="106" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A106" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+    </row>
+    <row r="107" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+    </row>
+    <row r="108" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+    </row>
+    <row r="109" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+    </row>
+    <row r="110" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+    </row>
+    <row r="111" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A111" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+    </row>
+    <row r="112" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+    </row>
+    <row r="113" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="3"/>
+    </row>
+    <row r="114" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="3"/>
+    </row>
+    <row r="115" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
